--- a/data/trans_bre/IP07_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP07_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,25</t>
+          <t>3,31</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-4,5%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 20,22</t>
+          <t>-1,44; 19,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 9,01</t>
+          <t>-15,76; 7,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 9,59</t>
+          <t>-13,56; 8,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-26,49; 12,6</t>
+          <t>-11,35; 18,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 32,81</t>
+          <t>-1,88; 31,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,25; 14,0</t>
+          <t>-20,72; 11,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 12,53</t>
+          <t>-15,59; 11,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-35,7; 18,47</t>
+          <t>-14,92; 28,64</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,76</t>
+          <t>1,7</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 5,81</t>
+          <t>-3,62; 5,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 6,94</t>
+          <t>-2,65; 6,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 5,45</t>
+          <t>-1,71; 5,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 10,68</t>
+          <t>-3,51; 7,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 7,84</t>
+          <t>-4,64; 7,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 9,69</t>
+          <t>-3,47; 9,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 6,46</t>
+          <t>-1,95; 6,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 15,07</t>
+          <t>-4,4; 10,05</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,17</t>
+          <t>-3,23</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-2,86%</t>
+          <t>-4,24%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 2,06</t>
+          <t>-11,32; 2,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 6,37</t>
+          <t>-9,28; 5,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 6,1</t>
+          <t>-5,85; 5,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 6,81</t>
+          <t>-11,81; 4,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 2,49</t>
+          <t>-13,23; 2,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 8,71</t>
+          <t>-11,46; 7,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 7,29</t>
+          <t>-6,66; 6,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 9,69</t>
+          <t>-14,99; 6,7</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 5,01</t>
+          <t>-2,75; 4,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 4,15</t>
+          <t>-3,37; 4,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 3,89</t>
+          <t>-1,7; 4,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 6,59</t>
+          <t>-3,6; 5,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 6,71</t>
+          <t>-3,5; 5,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 5,64</t>
+          <t>-4,4; 5,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 4,62</t>
+          <t>-1,92; 4,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 9,0</t>
+          <t>-4,63; 7,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP07_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP07_R-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>9,54</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-3,19</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,22</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,31</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,91%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-4,53%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-2,71%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>9.536186446782235</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-3.185215500357619</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-2.21917660591926</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3.310747376068535</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.1390735804785825</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.0452847079605356</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.02706417638738149</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.04660218037611975</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-1,44; 19,69</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-15,76; 7,84</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-13,56; 8,98</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-11,35; 18,35</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-1,88; 31,87</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-20,72; 11,55</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-15,59; 11,83</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-14,92; 28,64</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-1.437118860460564</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-15.76328864566522</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-13.56173768352043</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-11.35318360648043</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.01879133480118858</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.2071891349841541</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.1558513428231415</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.1492051473844529</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>19.68726445790035</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>7.839340864625818</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>8.98460532120043</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>18.35313633694222</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.3187340702596599</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.1155285410948931</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.1183414117753726</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.2864051111831337</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,12</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,24</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,21</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,7</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-3,62; 5,74</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-2,65; 6,96</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,71; 5,75</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-3,51; 7,33</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-4,64; 7,78</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-3,47; 9,73</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-1,95; 6,79</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-4,4; 10,05</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.117586849313135</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2.240247925587324</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.209209072681972</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.704886958201968</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.01473137544244792</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.03003621256730684</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.02559362003903875</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.02239614961217417</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-4,67</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,73</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-3,23</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-5,59%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-2,24%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-0,2%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-4,24%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-3.616961153370762</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.648674616851296</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.70798022685399</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.514209056340108</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.04637335670392807</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.03466479842817459</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.01946894732874896</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.04396288804704698</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-11,32; 2,12</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-9,28; 5,45</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-5,85; 5,23</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-11,81; 4,77</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-13,23; 2,64</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-11,46; 7,49</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-6,66; 6,28</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-14,99; 6,7</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5.74339457517068</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>6.963150799744278</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5.750776385283534</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>7.334448678067599</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.07778754990748375</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.09728438915272261</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.06785721535244614</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.1004839740988109</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +819,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,55</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,68</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-4.670089347148199</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.730198858897636</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.1688570929277655</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-3.23206129443222</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.05594058501543148</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.02241145911244048</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.001957465444487002</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.04242374681144701</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,75; 4,36</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,37; 4,36</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,7; 4,19</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-3,6; 5,47</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-3,5; 5,84</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-4,4; 5,99</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-1,92; 4,96</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-4,63; 7,59</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-11.32296247619373</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-9.282198822949086</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.847167592396286</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-11.80672074115152</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.1322662184994484</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1146411651758194</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.06663041764894245</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.149856489254198</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.123230796676931</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.451946978540443</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.230916862833566</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.767937524017853</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.02639258248606998</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.07491171442392142</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.06277944578186904</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.06696173877962357</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.9416795252471521</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.5457942340104993</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.284255026577197</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.6810164588115009</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.01228413287521494</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.007306234357629443</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.01494969563068265</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.008992993246264009</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.749412386895544</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.368609827720742</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.702993962960095</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-3.604776175570573</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.03499714162999828</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.04404363575172008</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.0191666009111353</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.04626622539319295</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>4.358116257130359</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.361328680149737</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.193498727192062</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>5.468234497961174</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.05842577407421011</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.05989546966172898</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.04959591304471775</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.07593666746519263</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1017,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
